--- a/deniz-dent/Deniz-Dent-Maliyet-Modeli.xlsx
+++ b/deniz-dent/Deniz-Dent-Maliyet-Modeli.xlsx
@@ -29,7 +29,7 @@
     <numFmt numFmtId="168" formatCode="#,##0.00 ₺"/>
     <numFmt numFmtId="169" formatCode="0.0&quot;x&quot;"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -107,6 +107,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00B91C1C"/>
       <sz val="10"/>
     </font>
@@ -165,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -206,6 +212,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1826,7 +1833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1940,7 +1947,7 @@
     <row r="9">
       <c r="A9" s="37" t="inlineStr">
         <is>
-          <t>B — Gelen çağrı Türk operatörden</t>
+          <t>B — Türk operatör + Twilio BYOC</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
@@ -1966,7 +1973,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Kliniğin hattı Türk SIP sağlayıcıyla bağlanır. Gelen dakika ücreti DÜŞER. Teklif alınmalı.</t>
+          <t>Kendi operatorumuz Twilio ya BYOC ile baglanir. Relay aynen calisir, kod degismez. Teklif alinmali.</t>
         </is>
       </c>
     </row>
@@ -2072,26 +2079,47 @@
     <row r="15">
       <c r="A15" s="38" t="inlineStr">
         <is>
+          <t>B senaryosu MİMARİ OLARAK DOĞRULANDI: Twilio BYOC (Bring Your Own Carrier) ile kendi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="39" t="inlineStr">
+        <is>
+          <t>operatörümüzü bağlayıp ConversationRelay i aynen kullanmaya devam edebiliyoruz — kod değişmiyor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>EKSİK: Twilio nun BYOC dakika ücreti. Twilio ya sorulacak, modele eklenecek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>ÖNEMLİ: B ve C senaryolarındaki dakika ücretleri VARSAYIMDIR. Türk SIP sağlayıcılardan</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="38" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="38" t="inlineStr">
         <is>
           <t>teklif alınmadan bu sayılar müşteriye verilmemelidir.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Yapay zekâ maliyeti neden küçük: görüşme başına yaklaşık 1 ₺. Model değiştirmek toplam</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>maliyeti ancak %4 oynatıyor. Telefon kalemi ise %76 — iyileştirme oraya yapılmalı.</t>
         </is>

--- a/deniz-dent/Deniz-Dent-Maliyet-Modeli.xlsx
+++ b/deniz-dent/Deniz-Dent-Maliyet-Modeli.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Fiyatlandirma" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Senaryolar" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Kaldiraclar" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Verimor" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,15 +22,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="$#,##0"/>
     <numFmt numFmtId="167" formatCode="#,##0 ₺"/>
     <numFmt numFmtId="168" formatCode="#,##0.00 ₺"/>
     <numFmt numFmtId="169" formatCode="0.0&quot;x&quot;"/>
+    <numFmt numFmtId="170" formatCode="$#,##0.000"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -116,6 +118,12 @@
       <color rgb="00B91C1C"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -171,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -214,6 +222,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2128,4 +2139,321 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Verimor Teklifi — 06.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Kaynak: Verimor e-postasi ve Bulut Santral fiyat listesi PDF. Fiyatlar KDV HARIC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="40" t="inlineStr">
+        <is>
+          <t>EN ÖNEMLİ MADDE: Verimor numaralarına gelen çağrılarda DAKİKA ÜCRETİ YOK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="39" t="inlineStr">
+        <is>
+          <t>Maliyetin en büyük kalemi (gelen çağrı dakikası) tamamen ortadan kalkıyor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>VERİMOR SABİT ÜCRETLER (₺/ay, KDV hariç)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Bulut Santral paketi</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="n">
+        <v>565</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>X Small: 5 kullanıcı / 3 dış hat, 6 aylık periyot (aylık 565 ₺)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>SIP Trunk modülü</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="n">
+        <v>899</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Aylık periyot. 6 aylıkta 824 ₺, 12 aylıkta 768 ₺</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>KDV oranı</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Verimor toplam (KDV dahil)</t>
+        </is>
+      </c>
+      <c r="B11" s="23">
+        <f>(B8+B9)*(1+B10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Gelen çağrı dakika ücreti</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Verimor: "gelen çağrılarda dakika başına ücretlendirme yansımaz"</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Numara taşıma / tahsis</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Taşıma ücretsiz. Yeni numara tahsisi 468 ₺ tek seferlik; ilk numara ücretsiz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Eşzamanlı kanal</t>
+        </is>
+      </c>
+      <c r="B15" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Artırılabilir. 100 çağrı/gün için yeterli (yoğun saatte bile ~1 kanal doluluk).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Taahhüt</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Yok. Ön ödemeli ilerliyor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>İKİ MİMARİ SEÇENEK</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>Seçenek</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>Relay $/dk</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>STT $/dk</t>
+        </is>
+      </c>
+      <c r="D19" s="28" t="inlineStr">
+        <is>
+          <t>Maliyet (₺/ay)</t>
+        </is>
+      </c>
+      <c r="E19" s="28" t="inlineStr">
+        <is>
+          <t>Çağrı başı (₺)</t>
+        </is>
+      </c>
+      <c r="F19" s="28" t="inlineStr">
+        <is>
+          <t>Önerilen fiyat (₺/ay)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="inlineStr">
+        <is>
+          <t>1 — Verimor → Twilio BYOC → Relay</t>
+        </is>
+      </c>
+      <c r="B20" s="42" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C20" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="33">
+        <f>($B$11)+(((Varsayimlar!B7*Varsayimlar!B9)*Varsayimlar!B8)*(B20+C20)+(Varsayimlar!B7*Varsayimlar!B9)*'Birim Maliyetler'!B14/1000*'Birim Maliyetler'!B13+(Varsayimlar!B7*Varsayimlar!B9)*((('Birim Maliyetler'!B25*'Birim Maliyetler'!B23)+('Birim Maliyetler'!B24*1.25))/1000000*INDEX('Birim Maliyetler'!B18:D18,Varsayimlar!B18)+('Birim Maliyetler'!B24*('Birim Maliyetler'!B23-1))/1000000*INDEX('Birim Maliyetler'!B20:D20,Varsayimlar!B18)+('Birim Maliyetler'!B26*'Birim Maliyetler'!B23)/1000000*INDEX('Birim Maliyetler'!B19:D19,Varsayimlar!B18))+'Birim Maliyetler'!B29)*Varsayimlar!B16</f>
+        <v/>
+      </c>
+      <c r="E20" s="32">
+        <f>IF((Varsayimlar!B7*Varsayimlar!B9)=0,0,D20/(Varsayimlar!B7*Varsayimlar!B9))</f>
+        <v/>
+      </c>
+      <c r="F20" s="31">
+        <f>(D20+Fiyatlandirma!$B$7)/(1-Varsayimlar!B17)</f>
+        <v/>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Kod DEĞİŞMEZ. Twilio BYOC dakika ücreti henüz bilinmiyor, eklenecek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="inlineStr">
+        <is>
+          <t>2 — Verimor → kendi medya katmanı</t>
+        </is>
+      </c>
+      <c r="B21" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="42" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D21" s="33">
+        <f>($B$11)+(((Varsayimlar!B7*Varsayimlar!B9)*Varsayimlar!B8)*(B21+C21)+(Varsayimlar!B7*Varsayimlar!B9)*'Birim Maliyetler'!B14/1000*'Birim Maliyetler'!B13+(Varsayimlar!B7*Varsayimlar!B9)*((('Birim Maliyetler'!B25*'Birim Maliyetler'!B23)+('Birim Maliyetler'!B24*1.25))/1000000*INDEX('Birim Maliyetler'!B18:D18,Varsayimlar!B18)+('Birim Maliyetler'!B24*('Birim Maliyetler'!B23-1))/1000000*INDEX('Birim Maliyetler'!B20:D20,Varsayimlar!B18)+('Birim Maliyetler'!B26*'Birim Maliyetler'!B23)/1000000*INDEX('Birim Maliyetler'!B19:D19,Varsayimlar!B18))+'Birim Maliyetler'!B29)*Varsayimlar!B16</f>
+        <v/>
+      </c>
+      <c r="E21" s="32">
+        <f>IF((Varsayimlar!B7*Varsayimlar!B9)=0,0,D21/(Varsayimlar!B7*Varsayimlar!B9))</f>
+        <v/>
+      </c>
+      <c r="F21" s="31">
+        <f>(D21+Fiyatlandirma!$B$7)/(1-Varsayimlar!B17)</f>
+        <v/>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Twilio tamamen çıkar. Verimor LiveKit + ElevenLabs entegrasyonunu belgeliyor. Geliştirme işi var.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>STT (konuşmayı metne çevirme) ücreti VARSAYIMDIR — $0,010/dk. Sağlayıcıdan teklif alınmadı.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>CEVAPLANMASI GEREKENLER</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>1. Twilio BYOC dakika ücreti nedir? (Seçenek 1 bunsuz tamamlanmıyor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>2. STT sağlayıcı ve fiyatı? (Seçenek 2 bunsuz tamamlanmıyor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>3. E-postadaki paket fiyatları (5.731 / 7.576 ₺) fiyat listesiyle eşleşmiyor — hangisi geçerli?</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>4. SIP Trunk modülü dışında başka zorunlu modül var mı?</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>5. WhatsApp: Verimor şu an yalnızca OTP gönderiyor; çift yönlü sohbet için Meta Cloud API gerekiyor.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/deniz-dent/Deniz-Dent-Maliyet-Modeli.xlsx
+++ b/deniz-dent/Deniz-Dent-Maliyet-Modeli.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Senaryolar" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Kaldiraclar" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Verimor" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="En Kotu Senaryo" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
     <numFmt numFmtId="169" formatCode="0.0&quot;x&quot;"/>
     <numFmt numFmtId="170" formatCode="$#,##0.000"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -124,6 +125,12 @@
       <color rgb="00047857"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000F766E"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -179,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -225,6 +232,28 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="16" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2456,4 +2485,713 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="78" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>En Kötü Senaryo — üç kademe</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Her kademe kendi varsayimlariyla bagimsiz hesaplanir. Sari hucreleri degistirebilirsiniz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>A = beklenen · B = kötü (hacim ve süre yüksek) · C = en kötü (her kalem aleyhimize)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Kademeler arasinda degisen tek sey varsayimlardir; formuller aynidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Varsayım</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>A — Beklenen</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>B — Kötü</t>
+        </is>
+      </c>
+      <c r="D7" s="43" t="inlineStr">
+        <is>
+          <t>C — En Kötü</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Neden bu değer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Günlük çağrı</t>
+        </is>
+      </c>
+      <c r="B8" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" s="44" t="n">
+        <v>150</v>
+      </c>
+      <c r="D8" s="44" t="n">
+        <v>200</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Klinik 100 dedi. Gerçek sayı bilinmiyor; 2 katına kadar açtık.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Ortalama süre (dakika)</t>
+        </is>
+      </c>
+      <c r="B9" s="45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C9" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Klinik tahmini 2,5. Yapay zekâ ilk aylarda daha uzun konuşur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Ayda gün</t>
+        </is>
+      </c>
+      <c r="B10" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="C10" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="D10" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>USD/TRY</t>
+        </is>
+      </c>
+      <c r="B11" s="45" t="n">
+        <v>50</v>
+      </c>
+      <c r="C11" s="45" t="n">
+        <v>55</v>
+      </c>
+      <c r="D11" s="45" t="n">
+        <v>60</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Kur riski bizde değil, modelde görünür olmalı.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>ConversationRelay ($/dk)</t>
+        </is>
+      </c>
+      <c r="B12" s="46" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C12" s="46" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D12" s="46" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Twilio liste fiyatı. Seçenek 2 de bu 0 olur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Twilio BYOC ($/dk)</t>
+        </is>
+      </c>
+      <c r="B13" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="46" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D13" s="46" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>BİLİNMİYOR. Twilio'ya soruldu. A'da 0 kabul edildi, B ve C'de ücret var varsayıldı.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Gelen çağrı (₺/dk)</t>
+        </is>
+      </c>
+      <c r="B14" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="47" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Verimor gelen dakikayı ücretsiz yazdı. C'de bu sözün tutmadığı varsayıldı.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Seslendirme ($/1.000 karakter)</t>
+        </is>
+      </c>
+      <c r="B15" s="46" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C15" s="46" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D15" s="46" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>ElevenLabs Flash. C'de daha pahalı modele geçildiği varsayıldı.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Görüşme başına karakter</t>
+        </is>
+      </c>
+      <c r="B16" s="44" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C16" s="44" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D16" s="44" t="n">
+        <v>2100</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Süreyle doğru orantılı.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Görüşme başına tur</t>
+        </is>
+      </c>
+      <c r="B17" s="44" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" s="44" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" s="44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Hasta–asistan karşılıklı konuşma sayısı.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Sistem metni (token)</t>
+        </is>
+      </c>
+      <c r="B18" s="44" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C18" s="44" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D18" s="44" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Klinik bilgisi büyüdükçe artar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Tur başına yeni girdi (token)</t>
+        </is>
+      </c>
+      <c r="B19" s="44" t="n">
+        <v>350</v>
+      </c>
+      <c r="C19" s="44" t="n">
+        <v>400</v>
+      </c>
+      <c r="D19" s="44" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Tur başına çıktı (token)</t>
+        </is>
+      </c>
+      <c r="B20" s="44" t="n">
+        <v>120</v>
+      </c>
+      <c r="C20" s="44" t="n">
+        <v>140</v>
+      </c>
+      <c r="D20" s="44" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Verimor sabit (₺/ay, KDV dahil)</t>
+        </is>
+      </c>
+      <c r="B21" s="48" t="n">
+        <v>1757</v>
+      </c>
+      <c r="C21" s="48" t="n">
+        <v>1757</v>
+      </c>
+      <c r="D21" s="48" t="n">
+        <v>7956</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>A ve B: fiyat listesi (X Small + SIP Trunk). C: e-postadaki yüksek rakam.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Sunucu + izleme ($/ay)</t>
+        </is>
+      </c>
+      <c r="B22" s="46" t="n">
+        <v>40</v>
+      </c>
+      <c r="C22" s="46" t="n">
+        <v>60</v>
+      </c>
+      <c r="D22" s="46" t="n">
+        <v>170</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>C: yedekli kurulum + LiveKit/medya sunucusu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>HESAPLANAN — SEÇENEK 1 (Twilio ConversationRelay kalıyor)</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Aylık çağrı</t>
+        </is>
+      </c>
+      <c r="B25" s="49">
+        <f>B8*B10</f>
+        <v/>
+      </c>
+      <c r="C25" s="49">
+        <f>C8*C10</f>
+        <v/>
+      </c>
+      <c r="D25" s="49">
+        <f>D8*D10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Aylık dakika</t>
+        </is>
+      </c>
+      <c r="B26" s="49">
+        <f>B25*B9</f>
+        <v/>
+      </c>
+      <c r="C26" s="49">
+        <f>C25*C9</f>
+        <v/>
+      </c>
+      <c r="D26" s="49">
+        <f>D25*D9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Telefon — Relay + BYOC</t>
+        </is>
+      </c>
+      <c r="B28" s="21">
+        <f>B26*(B12+B13)*B11</f>
+        <v/>
+      </c>
+      <c r="C28" s="21">
+        <f>C26*(C12+C13)*C11</f>
+        <v/>
+      </c>
+      <c r="D28" s="21">
+        <f>D26*(D12+D13)*D11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Telefon — gelen dakika</t>
+        </is>
+      </c>
+      <c r="B29" s="21">
+        <f>B26*B14</f>
+        <v/>
+      </c>
+      <c r="C29" s="21">
+        <f>C26*C14</f>
+        <v/>
+      </c>
+      <c r="D29" s="21">
+        <f>D26*D14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Telefon — Verimor sabit</t>
+        </is>
+      </c>
+      <c r="B30" s="21">
+        <f>B21</f>
+        <v/>
+      </c>
+      <c r="C30" s="21">
+        <f>C21</f>
+        <v/>
+      </c>
+      <c r="D30" s="21">
+        <f>D21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Seslendirme (ElevenLabs)</t>
+        </is>
+      </c>
+      <c r="B31" s="21">
+        <f>B25*B16/1000*B15*B11</f>
+        <v/>
+      </c>
+      <c r="C31" s="21">
+        <f>C25*C16/1000*C15*C11</f>
+        <v/>
+      </c>
+      <c r="D31" s="21">
+        <f>D25*D16/1000*D15*D11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Yapay zekâ (Claude Sonnet 5.5)</t>
+        </is>
+      </c>
+      <c r="B32" s="21">
+        <f>B25*((B19*B17+B18*1.25)/1000000*2+(B18*(B17-1))/1000000*0.2+(B20*B17)/1000000*10)*B11</f>
+        <v/>
+      </c>
+      <c r="C32" s="21">
+        <f>C25*((C19*C17+C18*1.25)/1000000*2+(C18*(C17-1))/1000000*0.2+(C20*C17)/1000000*10)*C11</f>
+        <v/>
+      </c>
+      <c r="D32" s="21">
+        <f>D25*((D19*D17+D18*1.25)/1000000*2+(D18*(D17-1))/1000000*0.2+(D20*D17)/1000000*10)*D11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Sunucu + izleme</t>
+        </is>
+      </c>
+      <c r="B33" s="21">
+        <f>B22*B11</f>
+        <v/>
+      </c>
+      <c r="C33" s="21">
+        <f>C22*C11</f>
+        <v/>
+      </c>
+      <c r="D33" s="21">
+        <f>D22*D11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>TOPLAM (₺/ay)</t>
+        </is>
+      </c>
+      <c r="B35" s="16">
+        <f>SUM(B28:B33)</f>
+        <v/>
+      </c>
+      <c r="C35" s="16">
+        <f>SUM(C28:C33)</f>
+        <v/>
+      </c>
+      <c r="D35" s="16">
+        <f>SUM(D28:D33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Çağrı başına (₺)</t>
+        </is>
+      </c>
+      <c r="B36" s="50">
+        <f>IF(B25=0,0,B35/B25)</f>
+        <v/>
+      </c>
+      <c r="C36" s="50">
+        <f>IF(C25=0,0,C35/C25)</f>
+        <v/>
+      </c>
+      <c r="D36" s="50">
+        <f>IF(D25=0,0,D35/D25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Dakika başına (₺)</t>
+        </is>
+      </c>
+      <c r="B37" s="50">
+        <f>IF(B26=0,0,B35/B26)</f>
+        <v/>
+      </c>
+      <c r="C37" s="50">
+        <f>IF(C26=0,0,C35/C26)</f>
+        <v/>
+      </c>
+      <c r="D37" s="50">
+        <f>IF(D26=0,0,D35/D26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Sabit kalemler (₺/ay)</t>
+        </is>
+      </c>
+      <c r="B38" s="21">
+        <f>B30+B33</f>
+        <v/>
+      </c>
+      <c r="C38" s="21">
+        <f>C30+C33</f>
+        <v/>
+      </c>
+      <c r="D38" s="21">
+        <f>D30+D33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Değişken — dakika başına (₺)</t>
+        </is>
+      </c>
+      <c r="B39" s="17">
+        <f>IF(B26=0,0,(B35-B38)/B26)</f>
+        <v/>
+      </c>
+      <c r="C39" s="17">
+        <f>IF(C26=0,0,(C35-C38)/C26)</f>
+        <v/>
+      </c>
+      <c r="D39" s="17">
+        <f>IF(D26=0,0,(D35-D38)/D26)</f>
+        <v/>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>EN ÖNEMLİ SATIR: maliyet neredeyse tamamen dakika başına. Fiyat da dakika başına kurulmalı.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>KARŞILAŞTIRMA — 7/24 İNSAN RESEPSİYON</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Haftada 168 saat · kişi başı 45 saat · izin/hastalık/bayram payı 1,2 kat = 4,5 kişi</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Kişi başı işveren maliyeti (₺/ay)</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>DOĞRULANMALI — 2026 işveren maliyeti teyit edilmeli. Bu hücre varsayımdır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Gereken kişi</t>
+        </is>
+      </c>
+      <c r="B44" s="51">
+        <f>168/45*1.2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>7/24 insan resepsiyon maliyeti (₺/ay)</t>
+        </is>
+      </c>
+      <c r="B45" s="52">
+        <f>B43*B44</f>
+        <v/>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Beklenen senaryo (A) bu rakamın belirgin altında. En kötü senaryo (C) ise aynı mertebeye çıkıyor —</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>yani asistanın maliyet avantajı garanti değil, çağrı hacmi ve dakika ücretine bağlı.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/deniz-dent/Deniz-Dent-Maliyet-Modeli.xlsx
+++ b/deniz-dent/Deniz-Dent-Maliyet-Modeli.xlsx
@@ -23,7 +23,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="$#,##0"/>
@@ -31,6 +31,7 @@
     <numFmt numFmtId="168" formatCode="#,##0.00 ₺"/>
     <numFmt numFmtId="169" formatCode="0.0&quot;x&quot;"/>
     <numFmt numFmtId="170" formatCode="$#,##0.000"/>
+    <numFmt numFmtId="171" formatCode="$#,##0.0000"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -186,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -242,6 +243,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2493,7 +2497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2669,18 +2673,18 @@
           <t>Twilio BYOC ($/dk)</t>
         </is>
       </c>
-      <c r="B13" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="46" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="D13" s="46" t="n">
-        <v>0.02</v>
+      <c r="B13" s="47" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="C13" s="47" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="D13" s="47" t="n">
+        <v>0.006</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>BİLİNMİYOR. Twilio'ya soruldu. A'da 0 kabul edildi, B ve C'de ücret var varsayıldı.</t>
+          <t>TEYİTLİ (Twilio, 07.10.2026): Türkiye BYOC trunking $0,0040/dk. C'de zam varsayıldı.</t>
         </is>
       </c>
     </row>
@@ -2690,13 +2694,13 @@
           <t>Gelen çağrı (₺/dk)</t>
         </is>
       </c>
-      <c r="B14" s="47" t="n">
+      <c r="B14" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="47" t="n">
+      <c r="C14" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="47" t="n">
+      <c r="D14" s="48" t="n">
         <v>0.2</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -2708,484 +2712,505 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Seslendirme ($/1.000 karakter)</t>
-        </is>
-      </c>
-      <c r="B15" s="46" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C15" s="46" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D15" s="46" t="n">
-        <v>0.08</v>
+          <t>Dakika yuvarlama (dk/çağrı)</t>
+        </is>
+      </c>
+      <c r="B15" s="45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C15" s="45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D15" s="45" t="n">
+        <v>0.5</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>ElevenLabs Flash. C'de daha pahalı modele geçildiği varsayıldı.</t>
+          <t>TEYİTLİ: Twilio kısmi dakikayı YUKARI yuvarlıyor. Süreler bir dağılıma yayıldığı için çağrı başına ortalama ~0,5 dk ekler.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Görüşme başına karakter</t>
-        </is>
-      </c>
-      <c r="B16" s="44" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C16" s="44" t="n">
-        <v>1800</v>
-      </c>
-      <c r="D16" s="44" t="n">
-        <v>2100</v>
+          <t>Seslendirme ($/1.000 karakter)</t>
+        </is>
+      </c>
+      <c r="B16" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="46" t="n">
+        <v>0.05</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Süreyle doğru orantılı.</t>
+          <t>TEYİTLİ: Seçenek 1'de TTS ConversationRelay içinde, ayrı sayaç yok. C'de ayrıca faturalandığı varsayıldı.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Görüşme başına tur</t>
+          <t>Görüşme başına karakter</t>
         </is>
       </c>
       <c r="B17" s="44" t="n">
-        <v>6</v>
+        <v>1500</v>
       </c>
       <c r="C17" s="44" t="n">
-        <v>8</v>
+        <v>1800</v>
       </c>
       <c r="D17" s="44" t="n">
-        <v>10</v>
+        <v>2100</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Hasta–asistan karşılıklı konuşma sayısı.</t>
+          <t>Yalnızca TTS ayrı faturalanırsa kullanılır.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Sistem metni (token)</t>
+          <t>Görüşme başına tur</t>
         </is>
       </c>
       <c r="B18" s="44" t="n">
-        <v>2500</v>
+        <v>6</v>
       </c>
       <c r="C18" s="44" t="n">
-        <v>3000</v>
+        <v>8</v>
       </c>
       <c r="D18" s="44" t="n">
-        <v>4000</v>
+        <v>10</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Klinik bilgisi büyüdükçe artar.</t>
+          <t>Hasta–asistan karşılıklı konuşma sayısı.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Tur başına yeni girdi (token)</t>
+          <t>Sistem metni (token)</t>
         </is>
       </c>
       <c r="B19" s="44" t="n">
-        <v>350</v>
+        <v>2500</v>
       </c>
       <c r="C19" s="44" t="n">
-        <v>400</v>
+        <v>3000</v>
       </c>
       <c r="D19" s="44" t="n">
-        <v>500</v>
+        <v>4000</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Klinik bilgisi büyüdükçe artar.</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Tur başına çıktı (token)</t>
+          <t>Tur başına yeni girdi (token)</t>
         </is>
       </c>
       <c r="B20" s="44" t="n">
-        <v>120</v>
+        <v>350</v>
       </c>
       <c r="C20" s="44" t="n">
-        <v>140</v>
+        <v>400</v>
       </c>
       <c r="D20" s="44" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Verimor sabit (₺/ay, KDV dahil)</t>
-        </is>
-      </c>
-      <c r="B21" s="48" t="n">
-        <v>1757</v>
-      </c>
-      <c r="C21" s="48" t="n">
-        <v>1757</v>
-      </c>
-      <c r="D21" s="48" t="n">
-        <v>7956</v>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>A ve B: fiyat listesi (X Small + SIP Trunk). C: e-postadaki yüksek rakam.</t>
-        </is>
+          <t>Tur başına çıktı (token)</t>
+        </is>
+      </c>
+      <c r="B21" s="44" t="n">
+        <v>120</v>
+      </c>
+      <c r="C21" s="44" t="n">
+        <v>140</v>
+      </c>
+      <c r="D21" s="44" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
+          <t>Verimor sabit (₺/ay, KDV dahil)</t>
+        </is>
+      </c>
+      <c r="B22" s="49" t="n">
+        <v>1757</v>
+      </c>
+      <c r="C22" s="49" t="n">
+        <v>1757</v>
+      </c>
+      <c r="D22" s="49" t="n">
+        <v>7956</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>A ve B: fiyat listesi (X Small + SIP Trunk). C: e-postadaki yüksek rakam.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
           <t>Sunucu + izleme ($/ay)</t>
         </is>
       </c>
-      <c r="B22" s="46" t="n">
+      <c r="B23" s="46" t="n">
         <v>40</v>
       </c>
-      <c r="C22" s="46" t="n">
+      <c r="C23" s="46" t="n">
         <v>60</v>
       </c>
-      <c r="D22" s="46" t="n">
+      <c r="D23" s="46" t="n">
         <v>170</v>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>C: yedekli kurulum + LiveKit/medya sunucusu.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>HESAPLANAN — SEÇENEK 1 (Twilio ConversationRelay kalıyor)</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Aylık çağrı</t>
-        </is>
-      </c>
-      <c r="B25" s="49">
-        <f>B8*B10</f>
-        <v/>
-      </c>
-      <c r="C25" s="49">
-        <f>C8*C10</f>
-        <v/>
-      </c>
-      <c r="D25" s="49">
-        <f>D8*D10</f>
-        <v/>
-      </c>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Aylık dakika</t>
-        </is>
-      </c>
-      <c r="B26" s="49">
-        <f>B25*B9</f>
-        <v/>
-      </c>
-      <c r="C26" s="49">
-        <f>C25*C9</f>
-        <v/>
-      </c>
-      <c r="D26" s="49">
-        <f>D25*D9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Telefon — Relay + BYOC</t>
-        </is>
-      </c>
-      <c r="B28" s="21">
-        <f>B26*(B12+B13)*B11</f>
-        <v/>
-      </c>
-      <c r="C28" s="21">
-        <f>C26*(C12+C13)*C11</f>
-        <v/>
-      </c>
-      <c r="D28" s="21">
-        <f>D26*(D12+D13)*D11</f>
+          <t>Aylık çağrı</t>
+        </is>
+      </c>
+      <c r="B26" s="50">
+        <f>B8*B10</f>
+        <v/>
+      </c>
+      <c r="C26" s="50">
+        <f>C8*C10</f>
+        <v/>
+      </c>
+      <c r="D26" s="50">
+        <f>D8*D10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Aylık faturalanan dakika</t>
+        </is>
+      </c>
+      <c r="B27" s="50">
+        <f>B26*(B9+B15)</f>
+        <v/>
+      </c>
+      <c r="C27" s="50">
+        <f>C26*(C9+C15)</f>
+        <v/>
+      </c>
+      <c r="D27" s="50">
+        <f>D26*(D9+D15)</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Telefon — gelen dakika</t>
+          <t>Telefon — Relay + BYOC</t>
         </is>
       </c>
       <c r="B29" s="21">
-        <f>B26*B14</f>
+        <f>B27*(B12+B13)*B11</f>
         <v/>
       </c>
       <c r="C29" s="21">
-        <f>C26*C14</f>
+        <f>C27*(C12+C13)*C11</f>
         <v/>
       </c>
       <c r="D29" s="21">
-        <f>D26*D14</f>
+        <f>D27*(D12+D13)*D11</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Telefon — Verimor sabit</t>
+          <t>Telefon — gelen dakika</t>
         </is>
       </c>
       <c r="B30" s="21">
-        <f>B21</f>
+        <f>B27*B14</f>
         <v/>
       </c>
       <c r="C30" s="21">
-        <f>C21</f>
+        <f>C27*C14</f>
         <v/>
       </c>
       <c r="D30" s="21">
-        <f>D21</f>
+        <f>D27*D14</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Seslendirme (ElevenLabs)</t>
+          <t>Telefon — Verimor sabit</t>
         </is>
       </c>
       <c r="B31" s="21">
-        <f>B25*B16/1000*B15*B11</f>
+        <f>B22</f>
         <v/>
       </c>
       <c r="C31" s="21">
-        <f>C25*C16/1000*C15*C11</f>
+        <f>C22</f>
         <v/>
       </c>
       <c r="D31" s="21">
-        <f>D25*D16/1000*D15*D11</f>
+        <f>D22</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Yapay zekâ (Claude Sonnet 5.5)</t>
+          <t>Seslendirme (ElevenLabs)</t>
         </is>
       </c>
       <c r="B32" s="21">
-        <f>B25*((B19*B17+B18*1.25)/1000000*2+(B18*(B17-1))/1000000*0.2+(B20*B17)/1000000*10)*B11</f>
+        <f>B26*B17/1000*B16*B11</f>
         <v/>
       </c>
       <c r="C32" s="21">
-        <f>C25*((C19*C17+C18*1.25)/1000000*2+(C18*(C17-1))/1000000*0.2+(C20*C17)/1000000*10)*C11</f>
+        <f>C26*C17/1000*C16*C11</f>
         <v/>
       </c>
       <c r="D32" s="21">
-        <f>D25*((D19*D17+D18*1.25)/1000000*2+(D18*(D17-1))/1000000*0.2+(D20*D17)/1000000*10)*D11</f>
+        <f>D26*D17/1000*D16*D11</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
+          <t>Yapay zekâ (Claude Sonnet 5.5)</t>
+        </is>
+      </c>
+      <c r="B33" s="21">
+        <f>B26*((B20*B18+B19*1.25)/1000000*2+(B19*(B18-1))/1000000*0.2+(B21*B18)/1000000*10)*B11</f>
+        <v/>
+      </c>
+      <c r="C33" s="21">
+        <f>C26*((C20*C18+C19*1.25)/1000000*2+(C19*(C18-1))/1000000*0.2+(C21*C18)/1000000*10)*C11</f>
+        <v/>
+      </c>
+      <c r="D33" s="21">
+        <f>D26*((D20*D18+D19*1.25)/1000000*2+(D19*(D18-1))/1000000*0.2+(D21*D18)/1000000*10)*D11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
           <t>Sunucu + izleme</t>
         </is>
       </c>
-      <c r="B33" s="21">
-        <f>B22*B11</f>
-        <v/>
-      </c>
-      <c r="C33" s="21">
-        <f>C22*C11</f>
-        <v/>
-      </c>
-      <c r="D33" s="21">
-        <f>D22*D11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="B34" s="21">
+        <f>B23*B11</f>
+        <v/>
+      </c>
+      <c r="C34" s="21">
+        <f>C23*C11</f>
+        <v/>
+      </c>
+      <c r="D34" s="21">
+        <f>D23*D11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>TOPLAM (₺/ay)</t>
         </is>
       </c>
-      <c r="B35" s="16">
-        <f>SUM(B28:B33)</f>
-        <v/>
-      </c>
-      <c r="C35" s="16">
-        <f>SUM(C28:C33)</f>
-        <v/>
-      </c>
-      <c r="D35" s="16">
-        <f>SUM(D28:D33)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Çağrı başına (₺)</t>
-        </is>
-      </c>
-      <c r="B36" s="50">
-        <f>IF(B25=0,0,B35/B25)</f>
-        <v/>
-      </c>
-      <c r="C36" s="50">
-        <f>IF(C25=0,0,C35/C25)</f>
-        <v/>
-      </c>
-      <c r="D36" s="50">
-        <f>IF(D25=0,0,D35/D25)</f>
+      <c r="B36" s="16">
+        <f>SUM(B29:B34)</f>
+        <v/>
+      </c>
+      <c r="C36" s="16">
+        <f>SUM(C29:C34)</f>
+        <v/>
+      </c>
+      <c r="D36" s="16">
+        <f>SUM(D29:D34)</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Dakika başına (₺)</t>
-        </is>
-      </c>
-      <c r="B37" s="50">
-        <f>IF(B26=0,0,B35/B26)</f>
-        <v/>
-      </c>
-      <c r="C37" s="50">
-        <f>IF(C26=0,0,C35/C26)</f>
-        <v/>
-      </c>
-      <c r="D37" s="50">
-        <f>IF(D26=0,0,D35/D26)</f>
+          <t>Çağrı başına (₺)</t>
+        </is>
+      </c>
+      <c r="B37" s="51">
+        <f>IF(B26=0,0,B36/B26)</f>
+        <v/>
+      </c>
+      <c r="C37" s="51">
+        <f>IF(C26=0,0,C36/C26)</f>
+        <v/>
+      </c>
+      <c r="D37" s="51">
+        <f>IF(D26=0,0,D36/D26)</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
+          <t>Faturalanan dakika başına (₺)</t>
+        </is>
+      </c>
+      <c r="B38" s="51">
+        <f>IF(B27=0,0,B36/B27)</f>
+        <v/>
+      </c>
+      <c r="C38" s="51">
+        <f>IF(C27=0,0,C36/C27)</f>
+        <v/>
+      </c>
+      <c r="D38" s="51">
+        <f>IF(D27=0,0,D36/D27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
           <t>Sabit kalemler (₺/ay)</t>
         </is>
       </c>
-      <c r="B38" s="21">
-        <f>B30+B33</f>
-        <v/>
-      </c>
-      <c r="C38" s="21">
-        <f>C30+C33</f>
-        <v/>
-      </c>
-      <c r="D38" s="21">
-        <f>D30+D33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="B39" s="21">
+        <f>B31+B34</f>
+        <v/>
+      </c>
+      <c r="C39" s="21">
+        <f>C31+C34</f>
+        <v/>
+      </c>
+      <c r="D39" s="21">
+        <f>D31+D34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>Değişken — dakika başına (₺)</t>
         </is>
       </c>
-      <c r="B39" s="17">
-        <f>IF(B26=0,0,(B35-B38)/B26)</f>
-        <v/>
-      </c>
-      <c r="C39" s="17">
-        <f>IF(C26=0,0,(C35-C38)/C26)</f>
-        <v/>
-      </c>
-      <c r="D39" s="17">
-        <f>IF(D26=0,0,(D35-D38)/D26)</f>
-        <v/>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="B40" s="17">
+        <f>IF(B27=0,0,(B36-B39)/B27)</f>
+        <v/>
+      </c>
+      <c r="C40" s="17">
+        <f>IF(C27=0,0,(C36-C39)/C27)</f>
+        <v/>
+      </c>
+      <c r="D40" s="17">
+        <f>IF(D27=0,0,(D36-D39)/D27)</f>
+        <v/>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>EN ÖNEMLİ SATIR: maliyet neredeyse tamamen dakika başına. Fiyat da dakika başına kurulmalı.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>KARŞILAŞTIRMA — 7/24 İNSAN RESEPSİYON</t>
         </is>
       </c>
-      <c r="B41" s="4" t="n"/>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Haftada 168 saat · kişi başı 45 saat · izin/hastalık/bayram payı 1,2 kat = 4,5 kişi</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>Kişi başı işveren maliyeti (₺/ay)</t>
-        </is>
-      </c>
-      <c r="B43" s="22" t="n">
-        <v>40000</v>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>DOĞRULANMALI — 2026 işveren maliyeti teyit edilmeli. Bu hücre varsayımdır.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
+          <t>Kişi başı işveren maliyeti (₺/ay)</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>DOĞRULANMALI — 2026 işveren maliyeti teyit edilmeli. Bu hücre varsayımdır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
           <t>Gereken kişi</t>
         </is>
       </c>
-      <c r="B44" s="51">
+      <c r="B45" s="52">
         <f>168/45*1.2</f>
         <v/>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>7/24 insan resepsiyon maliyeti (₺/ay)</t>
         </is>
       </c>
-      <c r="B45" s="52">
-        <f>B43*B44</f>
-        <v/>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="B46" s="53">
+        <f>B44*B45</f>
+        <v/>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Beklenen senaryo (A) bu rakamın belirgin altında. En kötü senaryo (C) ise aynı mertebeye çıkıyor —</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="E46" s="2" t="inlineStr">
+    <row r="47">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>yani asistanın maliyet avantajı garanti değil, çağrı hacmi ve dakika ücretine bağlı.</t>
         </is>
